--- a/artfynd/A 14108-2023 artfynd.xlsx
+++ b/artfynd/A 14108-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14108-2023 artfynd.xlsx
+++ b/artfynd/A 14108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96569027</v>
+        <v>96589659</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704965.4468254506</v>
+        <v>704993</v>
       </c>
       <c r="R2" t="n">
-        <v>7096149.093630662</v>
+        <v>7096135</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,53 +766,63 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
+          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96568987</v>
+        <v>96568995</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704989.1079404142</v>
+        <v>704952</v>
       </c>
       <c r="R3" t="n">
-        <v>7096098.161765873</v>
+        <v>7096143</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,37 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96589660</v>
+        <v>96568996</v>
       </c>
       <c r="B4" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>704995.9476790066</v>
+        <v>704943</v>
       </c>
       <c r="R4" t="n">
-        <v>7096135.219291337</v>
+        <v>7096143</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,86 +995,61 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
+          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96589662</v>
+        <v>96569017</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Västomån, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>705019.5120633492</v>
+        <v>704965</v>
       </c>
       <c r="R5" t="n">
-        <v>7096159.702598101</v>
+        <v>7096088</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,46 +1102,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
+          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96589661</v>
+        <v>96569018</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>705033.6426375866</v>
+        <v>704952</v>
       </c>
       <c r="R6" t="n">
-        <v>7096132.844415493</v>
+        <v>7096141</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,31 +1209,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Helmersson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
+          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1288,16 +1228,11 @@
         <v>96588625</v>
       </c>
       <c r="B7" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1310,12 +1245,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>704991.5861230006</v>
+        <v>704992</v>
       </c>
       <c r="R7" t="n">
-        <v>7096141.107569219</v>
+        <v>7096141</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1397,37 +1332,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96588632</v>
+        <v>96589660</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1437,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>704989.2014560401</v>
+        <v>704996</v>
       </c>
       <c r="R8" t="n">
-        <v>7096103.460682077</v>
+        <v>7096135</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1472,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,31 +1423,41 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Linnea Helmersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Olofsson, Jon Andersson, Linnea Helmersson</t>
+          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96589659</v>
+        <v>96589664</v>
       </c>
       <c r="B9" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,21 +1465,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>704992.8406769377</v>
+        <v>704944</v>
       </c>
       <c r="R9" t="n">
-        <v>7096135.456222339</v>
+        <v>7096165</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1584,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,6 +1573,1009 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96569020</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>705008</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7096035</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96589644</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>705014</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7096057</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96568987</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>704989</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7096098</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96588632</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>704989</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7096103</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson, Jon Andersson, Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>96589661</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>705034</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7096133</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>96589642</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>704961</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7096113</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>96589662</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>705019</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7096160</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linnea Helmersson, Jon Andersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>96569026</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>704970</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7096128</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96569027</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västomån, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>704966</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7096149</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-10-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jon Andersson, Linnea Helmersson, Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14108-2023 artfynd.xlsx
+++ b/artfynd/A 14108-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96589659</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96568995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96568996</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96569017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96569018</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96588625</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96589660</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96589664</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96569020</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96589644</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1894,6 +1949,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96568987</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96588632</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2123,6 +2188,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96589661</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2235,6 +2305,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96589642</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2362,6 +2437,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96589662</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2469,6 +2549,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96569026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,8 +2661,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96569027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>